--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487100_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487100_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8784</v>
+        <v>1.8248</v>
       </c>
       <c r="E2" t="n">
         <v>1.9209</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0426</v>
+        <v>-0.0961</v>
       </c>
       <c r="G2" t="n">
         <v>1.7501</v>
@@ -610,13 +610,13 @@
         <v>0.386</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2578</v>
+        <v>-0.3113</v>
       </c>
       <c r="T2" t="n">
         <v>-0.4164</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1586</v>
+        <v>0.1051</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4732</v>
+        <v>1.0518</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0839</v>
+        <v>2.7428</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6107</v>
+        <v>-1.691</v>
       </c>
       <c r="G3" t="n">
         <v>2.357</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3047</v>
+        <v>-0.7261</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1652</v>
+        <v>-0.5063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1395</v>
+        <v>-0.2198</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3234</v>
+        <v>0.377</v>
       </c>
       <c r="E4" t="n">
         <v>0.0207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3027</v>
+        <v>0.3563</v>
       </c>
       <c r="G4" t="n">
         <v>0.2877</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.186</v>
+        <v>-0.1127</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3446</v>
+        <v>-0.4854</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1586</v>
+        <v>0.3727</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0314</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7337</v>
+        <v>-0.6603</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1917</v>
+        <v>0.0509</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9254</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6162</v>
+        <v>-0.4645</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.881</v>
+        <v>-0.7026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2649</v>
+        <v>0.2381</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9714</v>
@@ -922,13 +922,13 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.4002</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3569</v>
+        <v>-0.1785</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.195</v>
+        <v>-0.2218</v>
       </c>
       <c r="V6" t="n">
         <v>0.3281</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3012</v>
+        <v>-1.168</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6042999999999999</v>
+        <v>1.4431</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9055</v>
+        <v>-2.6111</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9071</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1938</v>
+        <v>-1.0606</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2347</v>
+        <v>-0.3959</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9591</v>
+        <v>-0.6647</v>
       </c>
       <c r="V7" t="n">
         <v>1.7997</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4427</v>
+        <v>-2.0233</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2406</v>
+        <v>0.1788</v>
       </c>
       <c r="F8" t="n">
         <v>-2.2021</v>
@@ -1078,10 +1078,10 @@
         <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8302</v>
+        <v>-0.4108</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6398</v>
+        <v>-0.2204</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1904</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3164</v>
+        <v>-3.6572</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2309</v>
+        <v>-0.7076</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0855</v>
+        <v>-2.9496</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2143</v>
+        <v>-1.2348</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0641</v>
+        <v>-1.8682</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1503</v>
+        <v>0.6333</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8457</v>
+        <v>1.3209</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0514</v>
+        <v>-0.5591</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8971</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3686</v>
+        <v>-2.5558</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1155</v>
+        <v>-1.3091</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2531</v>
+        <v>-1.2467</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3841</v>
+        <v>-0.4224</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7681</v>
+        <v>-0.0985</v>
       </c>
       <c r="U9" t="n">
-        <v>0.616</v>
+        <v>-0.3239</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0699</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.496</v>
+        <v>-4.6719</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5464</v>
+        <v>-1.228</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9496</v>
+        <v>-3.4438</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2348</v>
+        <v>-1.9826</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8682</v>
+        <v>0.4772</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6333</v>
+        <v>-2.4598</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3209</v>
+        <v>-0.028</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5591</v>
+        <v>0.5175</v>
       </c>
       <c r="L10" t="n">
-        <v>1.88</v>
+        <v>-0.5455</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5558</v>
+        <v>-1.9546</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3091</v>
+        <v>-0.0403</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2467</v>
+        <v>-1.9143</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2612</v>
+        <v>0.0598</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9373</v>
+        <v>0.4442</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3239</v>
+        <v>-0.3844</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.228</v>
+        <v>-2.1701</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7641</v>
+        <v>-5.414</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.347</v>
+        <v>-1.9537</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4171</v>
+        <v>-3.4602</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9826</v>
+        <v>-4.2143</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4772</v>
+        <v>-1.0641</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4598</v>
+        <v>-3.1503</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.028</v>
+        <v>-1.8457</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5175</v>
+        <v>0.0514</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5455</v>
+        <v>-1.8971</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9546</v>
+        <v>-2.3686</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0403</v>
+        <v>-1.1155</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9143</v>
+        <v>-1.2531</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0324</v>
+        <v>0.2865</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3252</v>
+        <v>0.0453</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3576</v>
+        <v>0.2412</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1701</v>
+        <v>-0.3281</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4559</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.4476</v>
+        <v>-14.258</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03929999999999922</v>
+        <v>1.229000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.4869</v>
+        <v>-15.4868</v>
       </c>
       <c r="G12" t="n">
         <v>-4.498799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7025</v>
+        <v>1.702499999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-6.2014</v>
@@ -1378,7 +1378,7 @@
         <v>-5.644699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.032399999999999</v>
+        <v>-9.032400000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-5.7902</v>
@@ -1390,16 +1390,16 @@
         <v>11.5806</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7459</v>
+        <v>-3.5562</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4653</v>
+        <v>-1.2756</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2806</v>
+        <v>-2.2807</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4126999999999998</v>
+        <v>-0.4127</v>
       </c>
       <c r="W12" t="n">
         <v>9.697099999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.0451</v>
+        <v>8.2315</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8232</v>
+        <v>6.2237</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2219</v>
+        <v>2.0078</v>
       </c>
       <c r="G13" t="n">
         <v>3.6712</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.275</v>
+        <v>-0.0886</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7733</v>
+        <v>-0.3728</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4984</v>
+        <v>0.2842</v>
       </c>
       <c r="V13" t="n">
         <v>3.6839</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0078</v>
+        <v>2.9014</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3171</v>
+        <v>2.9165</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3093</v>
+        <v>-0.0151</v>
       </c>
       <c r="G14" t="n">
         <v>0.1897</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4714</v>
+        <v>1.3649</v>
       </c>
       <c r="T14" t="n">
-        <v>1.125</v>
+        <v>0.7245</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3463</v>
+        <v>0.6405</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1623</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.628</v>
+        <v>2.2132</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1291</v>
+        <v>1.9288</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4989</v>
+        <v>0.2844</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1516</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6095</v>
+        <v>1.1947</v>
       </c>
       <c r="T15" t="n">
-        <v>0.472</v>
+        <v>0.2717</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1375</v>
+        <v>0.923</v>
       </c>
       <c r="V15" t="n">
         <v>2.1701</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9643</v>
+        <v>2.2086</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4558</v>
+        <v>2.7882</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4915</v>
+        <v>-0.5796</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2757</v>
+        <v>0.2224</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9626</v>
+        <v>-2.6816</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6869</v>
+        <v>2.9039</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2742</v>
+        <v>1.4772</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7604</v>
+        <v>-1.713</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5137</v>
+        <v>3.1903</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5499</v>
+        <v>-1.2549</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.723</v>
+        <v>-0.9685</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8268</v>
+        <v>-0.2863</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0881</v>
+        <v>1.7371</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0881</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1562</v>
+        <v>0.7975</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5098</v>
+        <v>0.083</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6464</v>
+        <v>0.7145</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.0043</v>
+        <v>-0.5484</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6762</v>
+        <v>-1.7763</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.788</v>
+        <v>1.6409</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4845</v>
+        <v>1.2842</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3035</v>
+        <v>0.3567</v>
       </c>
       <c r="G17" t="n">
         <v>0.1746</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2076</v>
+        <v>1.0606</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8144</v>
+        <v>0.6141</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3933</v>
+        <v>0.4465</v>
       </c>
       <c r="V17" t="n">
         <v>1.9498</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6919</v>
+        <v>1.4504</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8869</v>
+        <v>2.7548</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.195</v>
+        <v>-1.3045</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2224</v>
+        <v>-0.2757</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6816</v>
+        <v>-0.9626</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9039</v>
+        <v>0.6869</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4772</v>
+        <v>2.2742</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.713</v>
+        <v>0.7604</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1903</v>
+        <v>1.5137</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2549</v>
+        <v>-2.5499</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9685</v>
+        <v>-1.723</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2863</v>
+        <v>-0.8268</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7371</v>
+        <v>3.0881</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7371</v>
+        <v>3.0881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7191</v>
+        <v>1.6422</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8183</v>
+        <v>0.8088</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.8335</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5484</v>
+        <v>-3.0043</v>
       </c>
       <c r="W18" t="n">
-        <v>1.228</v>
+        <v>-0.3281</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7763</v>
+        <v>-2.6762</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4794</v>
+        <v>0.5131</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6712</v>
+        <v>-0.7713</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1505</v>
+        <v>1.2844</v>
       </c>
       <c r="G19" t="n">
         <v>2.7816</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3721</v>
+        <v>-0.3384</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0873</v>
+        <v>-0.0129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4594</v>
+        <v>-0.3255</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.146</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0667</v>
+        <v>0.1668</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1522</v>
+        <v>-0.3128</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4953</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4719</v>
+        <v>0.4115</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2657</v>
+        <v>0.3659</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2062</v>
+        <v>0.0456</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8342000000000001</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5087</v>
+        <v>-1.3891</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0207</v>
+        <v>-1.8257</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5294</v>
+        <v>0.4365</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1327</v>
+        <v>-0.4853</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1262</v>
+        <v>0.2215</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0064</v>
+        <v>-0.7069</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0207</v>
+        <v>-0.659</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0207</v>
+        <v>0.0414</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7004</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1534</v>
+        <v>0.1737</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1469</v>
+        <v>0.1801</v>
       </c>
       <c r="O21" t="n">
         <v>-0.0064</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3411</v>
+        <v>-0.2898</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.2016</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3411</v>
+        <v>-0.0883</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5627</v>
+        <v>-1.5087</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0259</v>
+        <v>0.0207</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4633</v>
+        <v>-1.5294</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4853</v>
+        <v>-0.1327</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2215</v>
+        <v>-0.1262</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7069</v>
+        <v>-0.0064</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.659</v>
+        <v>0.0207</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0414</v>
+        <v>0.0207</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7004</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1737</v>
+        <v>-0.1534</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1801</v>
+        <v>-0.1469</v>
       </c>
       <c r="O22" t="n">
         <v>-0.0064</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4634</v>
+        <v>-0.3411</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4019</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0615</v>
+        <v>-0.3411</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>15.4476</v>
+        <v>16.1153</v>
       </c>
       <c r="E23" t="n">
-        <v>15.4869</v>
+        <v>15.4867</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.03929999999999995</v>
+        <v>0.6284000000000003</v>
       </c>
       <c r="G23" t="n">
         <v>4.498900000000001</v>
@@ -2218,13 +2218,13 @@
         <v>-1.702599999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>6.201300000000001</v>
+        <v>6.2013</v>
       </c>
       <c r="J23" t="n">
         <v>14.6771</v>
       </c>
       <c r="K23" t="n">
-        <v>5.644600000000001</v>
+        <v>5.6446</v>
       </c>
       <c r="L23" t="n">
         <v>9.032500000000001</v>
@@ -2233,13 +2233,13 @@
         <v>-10.1784</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.347099999999999</v>
+        <v>-7.347099999999998</v>
       </c>
       <c r="O23" t="n">
         <v>-2.831</v>
       </c>
       <c r="P23" t="n">
-        <v>5.7901</v>
+        <v>5.790099999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5804</v>
@@ -2248,22 +2248,22 @@
         <v>17.3708</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7459</v>
+        <v>5.4135</v>
       </c>
       <c r="T23" t="n">
         <v>2.2807</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4652</v>
+        <v>3.132900000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4126</v>
+        <v>0.4126000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>10.1097</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.697000000000001</v>
+        <v>-9.696999999999999</v>
       </c>
     </row>
   </sheetData>
